--- a/src/views/game/zlzq/cardList/xingkongCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/xingkongCard/z_level.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="11985" windowHeight="9795" firstSheet="2" activeTab="2"/>
+    <workbookView windowWidth="10080" windowHeight="10710"/>
   </bookViews>
   <sheets>
     <sheet name="帝国" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="78">
   <si>
     <t>名称</t>
   </si>
@@ -74,6 +74,9 @@
     <t>圣殿御卫</t>
   </si>
   <si>
+    <t>符文·民兵集结</t>
+  </si>
+  <si>
     <t>白袍主教</t>
   </si>
   <si>
@@ -83,160 +86,160 @@
     <t>召集护卫</t>
   </si>
   <si>
+    <t>紫色卡等：</t>
+  </si>
+  <si>
+    <t>曙光·安娜贝尔</t>
+  </si>
+  <si>
+    <t>圣枪·卡洛琳</t>
+  </si>
+  <si>
+    <t>明日之音·露娜</t>
+  </si>
+  <si>
+    <t>帝国军魂·莱哈特</t>
+  </si>
+  <si>
+    <t>正阳大主教·伊恩</t>
+  </si>
+  <si>
+    <t>钢铁统帅·雷蒙德</t>
+  </si>
+  <si>
+    <t>橙色卡等：</t>
+  </si>
+  <si>
+    <t>总计：</t>
+  </si>
+  <si>
+    <t>帝国卡等：</t>
+  </si>
+  <si>
+    <t>心灵黑洞1</t>
+  </si>
+  <si>
+    <t>心灵黑洞2</t>
+  </si>
+  <si>
+    <t>狡诈学徒</t>
+  </si>
+  <si>
+    <t>黑金勒索者</t>
+  </si>
+  <si>
+    <t>黑夜突袭</t>
+  </si>
+  <si>
+    <t>热血矿工</t>
+  </si>
+  <si>
+    <t>酗酒醉汉</t>
+  </si>
+  <si>
+    <t>不法交易</t>
+  </si>
+  <si>
+    <t>海燕精卫</t>
+  </si>
+  <si>
+    <t>黑金诈术师</t>
+  </si>
+  <si>
+    <t>花剑绅士·翔</t>
+  </si>
+  <si>
+    <t>海燕·鲍莉</t>
+  </si>
+  <si>
+    <t>赤影·艾希尔</t>
+  </si>
+  <si>
+    <t>魔卡幻术师·梅基</t>
+  </si>
+  <si>
+    <t>钢之咆哮·布瑞恩</t>
+  </si>
+  <si>
+    <t>港口卡等：</t>
+  </si>
+  <si>
+    <t>学仆-观测型</t>
+  </si>
+  <si>
+    <t>沉重否定1</t>
+  </si>
+  <si>
+    <t>沉重否定2</t>
+  </si>
+  <si>
+    <t>全数否定</t>
+  </si>
+  <si>
+    <t>隐形术</t>
+  </si>
+  <si>
+    <t>破魔系教授</t>
+  </si>
+  <si>
+    <t>克隆术1</t>
+  </si>
+  <si>
+    <t>克隆术2</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型</t>
+  </si>
+  <si>
+    <t>符文·邪月之夜</t>
+  </si>
+  <si>
+    <t>幻域秘树</t>
+  </si>
+  <si>
+    <t>学仆-塑钢型</t>
+  </si>
+  <si>
+    <t>观星台大预言家</t>
+  </si>
+  <si>
+    <t>米拉方舟</t>
+  </si>
+  <si>
+    <t>No.2时光·米拉</t>
+  </si>
+  <si>
+    <t>隐秘卡等：</t>
+  </si>
+  <si>
+    <t>飓风术</t>
+  </si>
+  <si>
+    <t>连击</t>
+  </si>
+  <si>
+    <t>铁山靠</t>
+  </si>
+  <si>
+    <t>风卷残云</t>
+  </si>
+  <si>
+    <t>蟠桃会</t>
+  </si>
+  <si>
+    <t>泰山之力</t>
+  </si>
+  <si>
+    <t>悟能禅杖</t>
+  </si>
+  <si>
+    <t>禅意卡等：</t>
+  </si>
+  <si>
+    <t>圣殿弩手</t>
+  </si>
+  <si>
     <t>炽阳坠落</t>
-  </si>
-  <si>
-    <t>紫色卡等：</t>
-  </si>
-  <si>
-    <t>曙光·安娜贝尔</t>
-  </si>
-  <si>
-    <t>圣枪·卡洛琳</t>
-  </si>
-  <si>
-    <t>明日之音·露娜</t>
-  </si>
-  <si>
-    <t>帝国军魂·莱哈特</t>
-  </si>
-  <si>
-    <t>正阳大主教·伊恩</t>
-  </si>
-  <si>
-    <t>钢铁统帅·雷蒙德</t>
-  </si>
-  <si>
-    <t>橙色卡等：</t>
-  </si>
-  <si>
-    <t>总计：</t>
-  </si>
-  <si>
-    <t>帝国卡等：</t>
-  </si>
-  <si>
-    <t>心灵黑洞1</t>
-  </si>
-  <si>
-    <t>心灵黑洞2</t>
-  </si>
-  <si>
-    <t>狡诈学徒</t>
-  </si>
-  <si>
-    <t>黑夜突袭</t>
-  </si>
-  <si>
-    <t>黑金勒索者</t>
-  </si>
-  <si>
-    <t>热血矿工</t>
-  </si>
-  <si>
-    <t>酗酒醉汉</t>
-  </si>
-  <si>
-    <t>不法交易</t>
-  </si>
-  <si>
-    <t>海燕精卫</t>
-  </si>
-  <si>
-    <t>黑金诈术师</t>
-  </si>
-  <si>
-    <t>花剑绅士·翔</t>
-  </si>
-  <si>
-    <t>海燕·鲍莉</t>
-  </si>
-  <si>
-    <t>赤影·艾希尔</t>
-  </si>
-  <si>
-    <t>魔卡幻术师·梅基</t>
-  </si>
-  <si>
-    <t>钢之咆哮·布瑞恩</t>
-  </si>
-  <si>
-    <t>港口卡等：</t>
-  </si>
-  <si>
-    <t>学仆-观测型</t>
-  </si>
-  <si>
-    <t>沉重否定1</t>
-  </si>
-  <si>
-    <t>沉重否定2</t>
-  </si>
-  <si>
-    <t>全数否定</t>
-  </si>
-  <si>
-    <t>隐形术</t>
-  </si>
-  <si>
-    <t>破魔系教授</t>
-  </si>
-  <si>
-    <t>克隆术1</t>
-  </si>
-  <si>
-    <t>克隆术2</t>
-  </si>
-  <si>
-    <t>学仆-脉冲型1</t>
-  </si>
-  <si>
-    <t>学仆-脉冲型2</t>
-  </si>
-  <si>
-    <t>幻域秘树</t>
-  </si>
-  <si>
-    <t>学仆-塑钢型</t>
-  </si>
-  <si>
-    <t>观星台大预言家</t>
-  </si>
-  <si>
-    <t>米拉方舟</t>
-  </si>
-  <si>
-    <t>No.2时光·米拉</t>
-  </si>
-  <si>
-    <t>隐秘卡等：</t>
-  </si>
-  <si>
-    <t>飓风术</t>
-  </si>
-  <si>
-    <t>连击</t>
-  </si>
-  <si>
-    <t>铁山靠</t>
-  </si>
-  <si>
-    <t>风卷残云</t>
-  </si>
-  <si>
-    <t>蟠桃会</t>
-  </si>
-  <si>
-    <t>泰山之力</t>
-  </si>
-  <si>
-    <t>悟能禅杖</t>
-  </si>
-  <si>
-    <t>禅意卡等：</t>
-  </si>
-  <si>
-    <t>圣殿弩手</t>
   </si>
   <si>
     <t>蒙面侠客·翔</t>
@@ -1375,10 +1378,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" s="2">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1389,7 +1392,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1397,10 +1400,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1411,7 +1414,7 @@
         <v>4</v>
       </c>
       <c r="C17" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1433,7 +1436,7 @@
       </c>
       <c r="C20" s="2">
         <f>AVERAGE(C11:C17)</f>
-        <v>22.2857142857143</v>
+        <v>21.4285714285714</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1444,7 +1447,7 @@
         <v>3</v>
       </c>
       <c r="C23" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1455,7 +1458,7 @@
         <v>4</v>
       </c>
       <c r="C24" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1477,7 +1480,7 @@
         <v>5</v>
       </c>
       <c r="C26" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1521,7 +1524,7 @@
       </c>
       <c r="C31" s="4">
         <f>AVERAGE(C23:C28)</f>
-        <v>21.8333333333333</v>
+        <v>22.3333333333333</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1533,14 +1536,14 @@
       </c>
       <c r="C34" s="5">
         <f>AVERAGE(C2:C5,C11:C17,C23:C28)</f>
-        <v>21.9411764705882</v>
+        <v>21.7647058823529</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C8 C34" formulaRange="1"/>
+    <ignoredError sqref="C34 C8" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1586,7 +1589,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1597,7 +1600,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1641,7 +1644,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1674,7 +1677,7 @@
       </c>
       <c r="C12" s="1">
         <f>AVERAGE(C2:C9)</f>
-        <v>21.125</v>
+        <v>21.75</v>
       </c>
       <c r="D12" s="2"/>
     </row>
@@ -1686,7 +1689,7 @@
         <v>2</v>
       </c>
       <c r="C15" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1719,7 +1722,7 @@
       </c>
       <c r="C19" s="2">
         <f>AVERAGE(C15:C16)</f>
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1730,7 +1733,7 @@
         <v>2</v>
       </c>
       <c r="C22" s="4">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1741,7 +1744,7 @@
         <v>3</v>
       </c>
       <c r="C23" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1752,7 +1755,7 @@
         <v>4</v>
       </c>
       <c r="C24" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1763,7 +1766,7 @@
         <v>4</v>
       </c>
       <c r="C25" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1774,7 +1777,7 @@
         <v>5</v>
       </c>
       <c r="C26" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1796,7 +1799,7 @@
       </c>
       <c r="C29" s="4">
         <f>AVERAGE(C22:C26)</f>
-        <v>18.6</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1808,7 +1811,7 @@
       </c>
       <c r="C32" s="5">
         <f>AVERAGE(C2:C9,C15:C16,C22:C26)</f>
-        <v>20.2</v>
+        <v>21.0666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -1847,7 +1850,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1880,7 +1883,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1902,7 +1905,7 @@
       </c>
       <c r="C8" s="1">
         <f>AVERAGE(C2:C5)</f>
-        <v>18.5</v>
+        <v>18.25</v>
       </c>
       <c r="D8" s="2"/>
     </row>
@@ -1969,7 +1972,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1991,7 +1994,7 @@
         <v>4</v>
       </c>
       <c r="C18" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2035,7 +2038,7 @@
       </c>
       <c r="C23" s="2">
         <f>AVERAGE(C11:C20)</f>
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -2080,7 +2083,7 @@
       </c>
       <c r="C32" s="5">
         <f>AVERAGE(C2:C5,C11:C20,C26:C26)</f>
-        <v>17.3333333333333</v>
+        <v>17.2</v>
       </c>
     </row>
   </sheetData>
@@ -2429,7 +2432,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -2440,7 +2443,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7" s="1">
         <v>2</v>
@@ -2572,7 +2575,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B22" s="2">
         <v>3</v>
@@ -2583,7 +2586,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B23" s="2">
         <v>3</v>
@@ -2594,7 +2597,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B24" s="2">
         <v>4</v>
@@ -2605,7 +2608,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="B25" s="2">
         <v>4</v>
@@ -2650,7 +2653,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B32" s="4">
         <v>2</v>
@@ -2661,7 +2664,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B33" s="4">
         <v>3</v>
@@ -2672,7 +2675,7 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B34" s="4">
         <v>3</v>
@@ -2683,7 +2686,7 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B35" s="4">
         <v>4</v>
@@ -2694,7 +2697,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B36" s="4">
         <v>4</v>
@@ -2716,7 +2719,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B38" s="4">
         <v>5</v>
@@ -2727,7 +2730,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B39" s="4">
         <v>5</v>
@@ -2738,7 +2741,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B40" s="4">
         <v>6</v>
@@ -2749,7 +2752,7 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B41" s="4">
         <v>8</v>
@@ -2785,7 +2788,7 @@
         <v>24</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C47" s="5">
         <f>AVERAGE(C2:C12,C18:C26,C32:C41)</f>

--- a/src/views/game/zlzq/cardList/xingkongCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/xingkongCard/z_level.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="10080" windowHeight="10710"/>
+    <workbookView windowWidth="12480" windowHeight="11265" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="帝国" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="78">
   <si>
     <t>名称</t>
   </si>
@@ -47,193 +47,193 @@
     <t>卡等</t>
   </si>
   <si>
+    <t>田园守望者</t>
+  </si>
+  <si>
+    <t>塔楼弓手</t>
+  </si>
+  <si>
+    <t>光明惩戒</t>
+  </si>
+  <si>
+    <t>小计：</t>
+  </si>
+  <si>
+    <t>蓝色卡等：</t>
+  </si>
+  <si>
+    <t>四芒军旗</t>
+  </si>
+  <si>
+    <t>传记·钢铁守卫</t>
+  </si>
+  <si>
+    <t>圣殿御卫</t>
+  </si>
+  <si>
+    <t>符文·民兵集结</t>
+  </si>
+  <si>
+    <t>白袍主教</t>
+  </si>
+  <si>
+    <t>圣殿骑士</t>
+  </si>
+  <si>
+    <t>召集护卫</t>
+  </si>
+  <si>
+    <t>紫色卡等：</t>
+  </si>
+  <si>
+    <t>曙光·安娜贝尔</t>
+  </si>
+  <si>
+    <t>圣枪·卡洛琳</t>
+  </si>
+  <si>
+    <t>明日之音·露娜</t>
+  </si>
+  <si>
+    <t>帝国军魂·莱哈特</t>
+  </si>
+  <si>
+    <t>正阳大主教·伊恩</t>
+  </si>
+  <si>
+    <t>钢铁统帅·雷蒙德</t>
+  </si>
+  <si>
+    <t>橙色卡等：</t>
+  </si>
+  <si>
+    <t>总计：</t>
+  </si>
+  <si>
+    <t>帝国卡等：</t>
+  </si>
+  <si>
+    <t>心灵黑洞1</t>
+  </si>
+  <si>
+    <t>心灵黑洞2</t>
+  </si>
+  <si>
+    <t>狡诈学徒</t>
+  </si>
+  <si>
+    <t>黑金勒索者</t>
+  </si>
+  <si>
+    <t>黑夜突袭</t>
+  </si>
+  <si>
+    <t>热血矿工</t>
+  </si>
+  <si>
+    <t>酗酒醉汉</t>
+  </si>
+  <si>
+    <t>不法交易</t>
+  </si>
+  <si>
+    <t>海燕精卫</t>
+  </si>
+  <si>
+    <t>黑金诈术师</t>
+  </si>
+  <si>
+    <t>花剑绅士·翔</t>
+  </si>
+  <si>
+    <t>海燕·鲍莉</t>
+  </si>
+  <si>
+    <t>赤影·艾希尔</t>
+  </si>
+  <si>
+    <t>魔卡幻术师·梅基</t>
+  </si>
+  <si>
+    <t>钢之咆哮·布瑞恩</t>
+  </si>
+  <si>
+    <t>港口卡等：</t>
+  </si>
+  <si>
+    <t>学仆-观测型</t>
+  </si>
+  <si>
+    <t>沉重否定1</t>
+  </si>
+  <si>
+    <t>沉重否定2</t>
+  </si>
+  <si>
+    <t>全数否定</t>
+  </si>
+  <si>
+    <t>隐形术</t>
+  </si>
+  <si>
+    <t>破魔系教授</t>
+  </si>
+  <si>
+    <t>克隆术1</t>
+  </si>
+  <si>
+    <t>克隆术2</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型</t>
+  </si>
+  <si>
+    <t>符文·邪月之夜</t>
+  </si>
+  <si>
+    <t>幻域秘树</t>
+  </si>
+  <si>
+    <t>学仆-塑钢型</t>
+  </si>
+  <si>
+    <t>观星台大预言家</t>
+  </si>
+  <si>
+    <t>米拉方舟</t>
+  </si>
+  <si>
+    <t>No.2时光·米拉</t>
+  </si>
+  <si>
+    <t>隐秘卡等：</t>
+  </si>
+  <si>
+    <t>飓风术</t>
+  </si>
+  <si>
+    <t>连击</t>
+  </si>
+  <si>
+    <t>铁山靠</t>
+  </si>
+  <si>
+    <t>风卷残云</t>
+  </si>
+  <si>
+    <t>蟠桃会</t>
+  </si>
+  <si>
+    <t>泰山之力</t>
+  </si>
+  <si>
+    <t>悟能禅杖</t>
+  </si>
+  <si>
+    <t>禅意卡等：</t>
+  </si>
+  <si>
     <t>圣殿斥候</t>
-  </si>
-  <si>
-    <t>田园守望者</t>
-  </si>
-  <si>
-    <t>塔楼弓手</t>
-  </si>
-  <si>
-    <t>光明惩戒</t>
-  </si>
-  <si>
-    <t>小计：</t>
-  </si>
-  <si>
-    <t>蓝色卡等：</t>
-  </si>
-  <si>
-    <t>四芒军旗</t>
-  </si>
-  <si>
-    <t>传记·钢铁守卫</t>
-  </si>
-  <si>
-    <t>圣殿御卫</t>
-  </si>
-  <si>
-    <t>符文·民兵集结</t>
-  </si>
-  <si>
-    <t>白袍主教</t>
-  </si>
-  <si>
-    <t>圣殿骑士</t>
-  </si>
-  <si>
-    <t>召集护卫</t>
-  </si>
-  <si>
-    <t>紫色卡等：</t>
-  </si>
-  <si>
-    <t>曙光·安娜贝尔</t>
-  </si>
-  <si>
-    <t>圣枪·卡洛琳</t>
-  </si>
-  <si>
-    <t>明日之音·露娜</t>
-  </si>
-  <si>
-    <t>帝国军魂·莱哈特</t>
-  </si>
-  <si>
-    <t>正阳大主教·伊恩</t>
-  </si>
-  <si>
-    <t>钢铁统帅·雷蒙德</t>
-  </si>
-  <si>
-    <t>橙色卡等：</t>
-  </si>
-  <si>
-    <t>总计：</t>
-  </si>
-  <si>
-    <t>帝国卡等：</t>
-  </si>
-  <si>
-    <t>心灵黑洞1</t>
-  </si>
-  <si>
-    <t>心灵黑洞2</t>
-  </si>
-  <si>
-    <t>狡诈学徒</t>
-  </si>
-  <si>
-    <t>黑金勒索者</t>
-  </si>
-  <si>
-    <t>黑夜突袭</t>
-  </si>
-  <si>
-    <t>热血矿工</t>
-  </si>
-  <si>
-    <t>酗酒醉汉</t>
-  </si>
-  <si>
-    <t>不法交易</t>
-  </si>
-  <si>
-    <t>海燕精卫</t>
-  </si>
-  <si>
-    <t>黑金诈术师</t>
-  </si>
-  <si>
-    <t>花剑绅士·翔</t>
-  </si>
-  <si>
-    <t>海燕·鲍莉</t>
-  </si>
-  <si>
-    <t>赤影·艾希尔</t>
-  </si>
-  <si>
-    <t>魔卡幻术师·梅基</t>
-  </si>
-  <si>
-    <t>钢之咆哮·布瑞恩</t>
-  </si>
-  <si>
-    <t>港口卡等：</t>
-  </si>
-  <si>
-    <t>学仆-观测型</t>
-  </si>
-  <si>
-    <t>沉重否定1</t>
-  </si>
-  <si>
-    <t>沉重否定2</t>
-  </si>
-  <si>
-    <t>全数否定</t>
-  </si>
-  <si>
-    <t>隐形术</t>
-  </si>
-  <si>
-    <t>破魔系教授</t>
-  </si>
-  <si>
-    <t>克隆术1</t>
-  </si>
-  <si>
-    <t>克隆术2</t>
-  </si>
-  <si>
-    <t>学仆-脉冲型</t>
-  </si>
-  <si>
-    <t>符文·邪月之夜</t>
-  </si>
-  <si>
-    <t>幻域秘树</t>
-  </si>
-  <si>
-    <t>学仆-塑钢型</t>
-  </si>
-  <si>
-    <t>观星台大预言家</t>
-  </si>
-  <si>
-    <t>米拉方舟</t>
-  </si>
-  <si>
-    <t>No.2时光·米拉</t>
-  </si>
-  <si>
-    <t>隐秘卡等：</t>
-  </si>
-  <si>
-    <t>飓风术</t>
-  </si>
-  <si>
-    <t>连击</t>
-  </si>
-  <si>
-    <t>铁山靠</t>
-  </si>
-  <si>
-    <t>风卷残云</t>
-  </si>
-  <si>
-    <t>蟠桃会</t>
-  </si>
-  <si>
-    <t>泰山之力</t>
-  </si>
-  <si>
-    <t>悟能禅杖</t>
-  </si>
-  <si>
-    <t>禅意卡等：</t>
   </si>
   <si>
     <t>圣殿弩手</t>
@@ -1253,7 +1253,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1278,10 +1278,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1300,22 +1300,16 @@
         <v>5</v>
       </c>
       <c r="B4" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4" s="1">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="1">
-        <v>5</v>
-      </c>
-      <c r="C5" s="1">
-        <v>20</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1"/>
@@ -1323,22 +1317,28 @@
       <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C7" s="1">
+        <f>AVERAGE(C2:C4)</f>
+        <v>21.6666666666667</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="1">
-        <f>AVERAGE(C2:C5)</f>
-        <v>21.5</v>
-      </c>
-      <c r="D8" s="2"/>
+      <c r="B10" s="2">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
@@ -1356,10 +1356,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1370,7 +1370,7 @@
         <v>2</v>
       </c>
       <c r="C13" s="2">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1378,10 +1378,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" s="2">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1392,7 +1392,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1400,22 +1400,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" s="2">
         <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="2">
-        <v>4</v>
-      </c>
-      <c r="C17" s="2">
-        <v>22</v>
-      </c>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2"/>
@@ -1423,20 +1417,26 @@
       <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="2" t="s">
+      <c r="A19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="2">
+        <f>AVERAGE(C10:C16)</f>
+        <v>22.4285714285714</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="2">
-        <f>AVERAGE(C11:C17)</f>
-        <v>21.4285714285714</v>
+      <c r="B22" s="4">
+        <v>3</v>
+      </c>
+      <c r="C22" s="4">
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1444,10 +1444,10 @@
         <v>17</v>
       </c>
       <c r="B23" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C23" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1458,7 +1458,7 @@
         <v>4</v>
       </c>
       <c r="C24" s="4">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1466,10 +1466,10 @@
         <v>19</v>
       </c>
       <c r="B25" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" s="4">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1477,7 +1477,7 @@
         <v>20</v>
       </c>
       <c r="B26" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C26" s="4">
         <v>24</v>
@@ -1488,22 +1488,16 @@
         <v>21</v>
       </c>
       <c r="B27" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C27" s="4">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" s="4">
-        <v>8</v>
-      </c>
-      <c r="C28" s="4">
-        <v>21</v>
-      </c>
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="4"/>
@@ -1511,39 +1505,34 @@
       <c r="C29" s="4"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B31" s="4" t="s">
+      <c r="A30" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" s="4">
+        <f>AVERAGE(C22:C27)</f>
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C31" s="4">
-        <f>AVERAGE(C23:C28)</f>
-        <v>22.3333333333333</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="5" t="s">
+      <c r="B33" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C34" s="5">
-        <f>AVERAGE(C2:C5,C11:C17,C23:C28)</f>
-        <v>21.7647058823529</v>
+      <c r="C33" s="5">
+        <f>AVERAGE(C2:C4,C10:C16,C22:C27)</f>
+        <v>22.3125</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C34 C8" formulaRange="1"/>
+    <ignoredError sqref="C7 C33" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1572,7 +1561,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -1583,7 +1572,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
@@ -1594,7 +1583,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -1605,7 +1594,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -1616,7 +1605,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -1627,7 +1616,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
@@ -1638,7 +1627,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
@@ -1649,7 +1638,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
@@ -1670,10 +1659,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="C12" s="1">
         <f>AVERAGE(C2:C9)</f>
@@ -1683,7 +1672,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" s="2">
         <v>2</v>
@@ -1694,13 +1683,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B16" s="2">
         <v>4</v>
       </c>
       <c r="C16" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1715,19 +1704,19 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C19" s="2">
         <f>AVERAGE(C15:C16)</f>
-        <v>21.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B22" s="4">
         <v>2</v>
@@ -1738,18 +1727,18 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B23" s="4">
         <v>3</v>
       </c>
       <c r="C23" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B24" s="4">
         <v>4</v>
@@ -1760,7 +1749,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B25" s="4">
         <v>4</v>
@@ -1771,13 +1760,13 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B26" s="4">
         <v>5</v>
       </c>
       <c r="C26" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1792,26 +1781,26 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C29" s="4">
         <f>AVERAGE(C22:C26)</f>
-        <v>19.8</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32" s="5">
         <f>AVERAGE(C2:C9,C15:C16,C22:C26)</f>
-        <v>21.0666666666667</v>
+        <v>21.2666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -1844,7 +1833,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
@@ -1855,7 +1844,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -1866,7 +1855,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -1877,7 +1866,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B5" s="1">
         <v>3</v>
@@ -1898,10 +1887,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="C8" s="1">
         <f>AVERAGE(C2:C5)</f>
@@ -1911,18 +1900,18 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
       </c>
       <c r="C11" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
@@ -1933,7 +1922,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B13" s="2">
         <v>2</v>
@@ -1944,7 +1933,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B14" s="2">
         <v>2</v>
@@ -1955,7 +1944,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B15" s="2">
         <v>3</v>
@@ -1966,7 +1955,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B16" s="2">
         <v>3</v>
@@ -1977,7 +1966,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B17" s="2">
         <v>4</v>
@@ -1988,7 +1977,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B18" s="2">
         <v>4</v>
@@ -1999,7 +1988,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B19" s="2">
         <v>5</v>
@@ -2010,7 +1999,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B20" s="2">
         <v>7</v>
@@ -2031,19 +2020,19 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C23" s="2">
         <f>AVERAGE(C11:C20)</f>
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B26" s="4">
         <v>5</v>
@@ -2064,10 +2053,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C29" s="4">
         <f>AVERAGE(C26:C26)</f>
@@ -2076,14 +2065,14 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C32" s="5">
         <f>AVERAGE(C2:C5,C11:C20,C26:C26)</f>
-        <v>17.2</v>
+        <v>17.2666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -2116,7 +2105,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
@@ -2127,7 +2116,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -2138,7 +2127,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -2149,7 +2138,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B5" s="1">
         <v>3</v>
@@ -2160,7 +2149,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -2171,7 +2160,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
@@ -2182,7 +2171,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
@@ -2193,7 +2182,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
@@ -2204,7 +2193,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B10" s="1">
         <v>3</v>
@@ -2215,7 +2204,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B11" s="1">
         <v>4</v>
@@ -2226,7 +2215,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B12" s="1">
         <v>4</v>
@@ -2237,7 +2226,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B13" s="1">
         <v>4</v>
@@ -2258,10 +2247,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="C16" s="1">
         <f>AVERAGE(C2:C13)</f>
@@ -2271,7 +2260,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B19" s="2">
         <v>4</v>
@@ -2282,7 +2271,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B20" s="2">
         <v>4</v>
@@ -2303,10 +2292,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C23" s="2">
         <f>AVERAGE(C19:C20)</f>
@@ -2315,7 +2304,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B26" s="4">
         <v>4</v>
@@ -2336,10 +2325,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C29" s="4">
         <f>AVERAGE(C26:C26)</f>
@@ -2348,10 +2337,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C32" s="5">
         <f>AVERAGE(C2:C13,C19:C20,C26:C26)</f>
@@ -2388,7 +2377,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -2399,7 +2388,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
@@ -2410,7 +2399,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
@@ -2421,7 +2410,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -2432,7 +2421,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -2443,7 +2432,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7" s="1">
         <v>2</v>
@@ -2465,7 +2454,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
@@ -2476,7 +2465,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" s="1">
         <v>3</v>
@@ -2487,7 +2476,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B11" s="1">
         <v>3</v>
@@ -2498,7 +2487,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B12" s="1">
         <v>5</v>
@@ -2519,10 +2508,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="C15" s="1">
         <f>AVERAGE(C2:C12)</f>
@@ -2531,7 +2520,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B18" s="2">
         <v>1</v>
@@ -2542,7 +2531,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B19" s="2">
         <v>1</v>
@@ -2553,7 +2542,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B20" s="2">
         <v>2</v>
@@ -2564,7 +2553,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B21" s="2">
         <v>2</v>
@@ -2575,7 +2564,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B22" s="2">
         <v>3</v>
@@ -2586,7 +2575,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B23" s="2">
         <v>3</v>
@@ -2597,7 +2586,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B24" s="2">
         <v>4</v>
@@ -2619,7 +2608,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="2">
         <v>4</v>
@@ -2641,10 +2630,10 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C29" s="2">
         <f>AVERAGE(C18:C26)</f>
@@ -2708,7 +2697,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B37" s="4">
         <v>4</v>
@@ -2773,10 +2762,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C44" s="4">
         <f>AVERAGE(C32:C41)</f>
@@ -2785,7 +2774,7 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>77</v>
